--- a/tests/fmudesign/data/config/generateddesignmatrix.xlsx
+++ b/tests/fmudesign/data/config/generateddesignmatrix.xlsx
@@ -3765,14 +3765,14 @@
         <v>3.312761361462417</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8922653228443025</v>
+        <v>0.3405451602582412</v>
       </c>
       <c r="M42" t="n">
-        <v>2.490909188126159</v>
+        <v>1.699171350359906</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3842,17 +3842,17 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>4.408444393814364</v>
+        <v>3.596000397687326</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7142972820942644</v>
+        <v>0.4399133031006102</v>
       </c>
       <c r="M43" t="n">
-        <v>4.062824687762893</v>
+        <v>3.633797788134383</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2018-11-02</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3922,17 +3922,17 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2.906806204300374</v>
+        <v>4.557569414071397</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3899511547792094</v>
+        <v>0.5322097950003604</v>
       </c>
       <c r="M44" t="n">
-        <v>1.814233423942025</v>
+        <v>4.722993614566714</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2018-11-04</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4002,17 +4002,17 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>2.678603372562655</v>
+        <v>2.010129862683775</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5952129542012938</v>
+        <v>0.9387502381193247</v>
       </c>
       <c r="M45" t="n">
-        <v>2.102029294608303</v>
+        <v>3.894616397188516</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2018-11-04</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4082,17 +4082,17 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1.970884398409216</v>
+        <v>2.957179938030218</v>
       </c>
       <c r="L46" t="n">
-        <v>0.06997952232872831</v>
+        <v>0.003162024706935285</v>
       </c>
       <c r="M46" t="n">
-        <v>3.270997562251554</v>
+        <v>3.0135482484776</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4162,17 +4162,17 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1.452300815137419</v>
+        <v>3.850028470828336</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1924493132797433</v>
+        <v>0.1093936923621152</v>
       </c>
       <c r="M47" t="n">
-        <v>2.689969559988407</v>
+        <v>2.094985869194099</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2018-11-02</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4242,17 +4242,17 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>3.160235428392756</v>
+        <v>2.736961600233399</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9721230429778851</v>
+        <v>0.6027076791813784</v>
       </c>
       <c r="M48" t="n">
-        <v>3.000004124067567</v>
+        <v>2.575046529781941</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2018-11-04</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4322,17 +4322,17 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3.540487636857445</v>
+        <v>3.109612397707986</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4508303319003345</v>
+        <v>0.7452597618235484</v>
       </c>
       <c r="M49" t="n">
-        <v>2.91638266655234</v>
+        <v>3.24474570815607</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -4402,17 +4402,17 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>4.014728423765151</v>
+        <v>1.729450733522048</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2037217458507197</v>
+        <v>0.8396129844741591</v>
       </c>
       <c r="M50" t="n">
-        <v>4.841562635511835</v>
+        <v>2.790375261341003</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-02</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -4482,17 +4482,17 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>2.307763212729425</v>
+        <v>2.239917059875281</v>
       </c>
       <c r="L51" t="n">
-        <v>0.6070211047654768</v>
+        <v>0.2777100846249964</v>
       </c>
       <c r="M51" t="n">
-        <v>3.717597952802628</v>
+        <v>2.384889884889029</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2018-11-02</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4576,16 +4576,16 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>4.52</v>
+        <v>0.22</v>
       </c>
       <c r="P52" t="n">
-        <v>0.666</v>
+        <v>0.256</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.239477671346626</v>
+        <v>3.645333065471997</v>
       </c>
       <c r="R52" t="n">
-        <v>2.474116253235223</v>
+        <v>3.497679760136819</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4656,16 +4656,16 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="P53" t="n">
-        <v>0.349</v>
+        <v>0.043</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.925617475650472</v>
+        <v>1.498844947262842</v>
       </c>
       <c r="R53" t="n">
-        <v>3.494092805011585</v>
+        <v>6.355352158851318</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4736,16 +4736,16 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0.05</v>
+        <v>0.643</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.730220013400182</v>
+        <v>2.995423174271814</v>
       </c>
       <c r="R54" t="n">
-        <v>5.266093711797867</v>
+        <v>2.469408079691926</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -4816,16 +4816,16 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.51</v>
+        <v>2.96</v>
       </c>
       <c r="P55" t="n">
-        <v>0.308</v>
+        <v>0.859</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4487595588066</v>
+        <v>4.007145365558142</v>
       </c>
       <c r="R55" t="n">
-        <v>6.221460645346724</v>
+        <v>1.313291241856839</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="P56" t="n">
-        <v>0.267</v>
+        <v>0.136</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.813504166702091</v>
+        <v>2.397914017748739</v>
       </c>
       <c r="R56" t="n">
-        <v>8.504226502300446</v>
+        <v>2.551850809947167</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -4976,16 +4976,16 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="P57" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.758</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.822175768038527</v>
+        <v>3.467068657554671</v>
       </c>
       <c r="R57" t="n">
-        <v>4.315872398238649</v>
+        <v>6.931100406207087</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -5056,16 +5056,16 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0.379</v>
+        <v>0.269</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.593966821832412</v>
+        <v>3.034151111937381</v>
       </c>
       <c r="R58" t="n">
-        <v>1.245251147125175</v>
+        <v>1.814473923825558</v>
       </c>
       <c r="S58" t="n">
         <v>6</v>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
       <c r="P59" t="n">
-        <v>0.075</v>
+        <v>0.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.699555915741093</v>
+        <v>3.110887857870795</v>
       </c>
       <c r="R59" t="n">
-        <v>4.729371097386275</v>
+        <v>2.864510510985731</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -5216,16 +5216,16 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="P60" t="n">
-        <v>0.455</v>
+        <v>0.17</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.092932400354139</v>
+        <v>2.319499271200968</v>
       </c>
       <c r="R60" t="n">
-        <v>9.638010158813792</v>
+        <v>1.856610477374468</v>
       </c>
       <c r="S60" t="n">
         <v>8</v>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.28</v>
+        <v>1.73</v>
       </c>
       <c r="P61" t="n">
-        <v>0.167</v>
+        <v>0.462</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.463815111836193</v>
+        <v>2.147034623891099</v>
       </c>
       <c r="R61" t="n">
-        <v>1.722534369974754</v>
+        <v>4.469683558025049</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -5376,16 +5376,16 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="P62" t="n">
-        <v>0.739</v>
+        <v>0.733</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.718731603749992</v>
+        <v>3.884508318357508</v>
       </c>
       <c r="R62" t="n">
-        <v>1.144922810495005</v>
+        <v>9.288226062495578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -5456,16 +5456,16 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>2.04</v>
+        <v>0.66</v>
       </c>
       <c r="P63" t="n">
-        <v>0.702</v>
+        <v>0.363</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.186149849951476</v>
+        <v>2.710014373510555</v>
       </c>
       <c r="R63" t="n">
-        <v>2.085619469384973</v>
+        <v>1.630039135018941</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="P64" t="n">
-        <v>0.503</v>
+        <v>0.671</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.000343136400176</v>
+        <v>2.932095252343425</v>
       </c>
       <c r="R64" t="n">
-        <v>1.979783089661514</v>
+        <v>3.276857513437453</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -5612,16 +5612,16 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>1.82</v>
+        <v>0.26</v>
       </c>
       <c r="P65" t="n">
-        <v>0.836</v>
+        <v>0.031</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.52139882242179</v>
+        <v>2.516903321957964</v>
       </c>
       <c r="R65" t="n">
-        <v>3.72357036094949</v>
+        <v>1.365933980697398</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>3.05</v>
+        <v>0.74</v>
       </c>
       <c r="P66" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.956717592763502</v>
+        <v>3.237461074512055</v>
       </c>
       <c r="R66" t="n">
-        <v>8.894152686677597</v>
+        <v>8.309568406616675</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5768,16 +5768,16 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01</v>
+        <v>0.323</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.336086656658634</v>
+        <v>3.442182000171787</v>
       </c>
       <c r="R67" t="n">
-        <v>7.400469490658218</v>
+        <v>1.128575814988517</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5846,16 +5846,16 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>1.6</v>
+        <v>0.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0.972</v>
+        <v>0.408</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.848790750366065</v>
+        <v>2.841827384585128</v>
       </c>
       <c r="R68" t="n">
-        <v>2.62860451091307</v>
+        <v>5.923904377385364</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -5924,16 +5924,16 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="P69" t="n">
-        <v>0.116</v>
+        <v>0.469</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.030349152328206</v>
+        <v>3.604597731997663</v>
       </c>
       <c r="R69" t="n">
-        <v>1.066577147230623</v>
+        <v>7.879746307055707</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -6002,16 +6002,16 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>2.52</v>
+        <v>7.03</v>
       </c>
       <c r="P70" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.026147697843917</v>
+        <v>4.206947193677941</v>
       </c>
       <c r="R70" t="n">
-        <v>5.670629015585138</v>
+        <v>3.15068015913762</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6080,16 +6080,16 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.74</v>
+        <v>2.57</v>
       </c>
       <c r="P71" t="n">
-        <v>0.432</v>
+        <v>0.523</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.314176424686048</v>
+        <v>1.95109954130258</v>
       </c>
       <c r="R71" t="n">
-        <v>2.184784174669904</v>
+        <v>4.226298775885541</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -6158,16 +6158,16 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>2.26</v>
+        <v>0.36</v>
       </c>
       <c r="P72" t="n">
-        <v>0.597</v>
+        <v>0.104</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.764782971700157</v>
+        <v>2.602016160561055</v>
       </c>
       <c r="R72" t="n">
-        <v>6.545672123841459</v>
+        <v>1.47993948880455</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -6236,16 +6236,16 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.55</v>
+        <v>5.2</v>
       </c>
       <c r="P73" t="n">
-        <v>0.228</v>
+        <v>0.918</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.597257954940388</v>
+        <v>3.741895121297341</v>
       </c>
       <c r="R73" t="n">
-        <v>3.158571170719802</v>
+        <v>8.776673540877217</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>3.89</v>
+        <v>3.21</v>
       </c>
       <c r="P74" t="n">
-        <v>0.486</v>
+        <v>0.797</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.084615425347334</v>
+        <v>2.750992156841556</v>
       </c>
       <c r="R74" t="n">
-        <v>1.341628701735398</v>
+        <v>5.006674846071206</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="P75" t="n">
-        <v>0.896</v>
+        <v>0.948</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.228320203741967</v>
+        <v>4.314158803755637</v>
       </c>
       <c r="R75" t="n">
-        <v>1.483537024854461</v>
+        <v>1.040623918684137</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>6.58</v>
+        <v>1.87</v>
       </c>
       <c r="P76" t="n">
-        <v>0.604</v>
+        <v>0.805</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.86092445747804</v>
+        <v>3.310544311795028</v>
       </c>
       <c r="R76" t="n">
-        <v>3.395821331238111</v>
+        <v>1.170797449177683</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -6548,16 +6548,16 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.62</v>
+        <v>4.31</v>
       </c>
       <c r="P77" t="n">
-        <v>0.195</v>
+        <v>0.542</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.304601714989863</v>
+        <v>1.710129568329226</v>
       </c>
       <c r="R77" t="n">
-        <v>4.181959772192657</v>
+        <v>2.302854002526989</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6626,16 +6626,16 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>1.02</v>
+        <v>0.06</v>
       </c>
       <c r="P78" t="n">
-        <v>0.793</v>
+        <v>0.068</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.87727905483843</v>
+        <v>3.143661923525657</v>
       </c>
       <c r="R78" t="n">
-        <v>1.588809407409278</v>
+        <v>5.604814992150383</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6704,16 +6704,16 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.3</v>
+        <v>1.42</v>
       </c>
       <c r="P79" t="n">
-        <v>0.552</v>
+        <v>0.888</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.401154656660488</v>
+        <v>4.954078013363532</v>
       </c>
       <c r="R79" t="n">
-        <v>2.790672564239211</v>
+        <v>5.383002986433275</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -6782,16 +6782,16 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="P80" t="n">
-        <v>0.914</v>
+        <v>0.367</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.162079958040669</v>
+        <v>2.263164269486234</v>
       </c>
       <c r="R80" t="n">
-        <v>7.245270439615315</v>
+        <v>3.699542221911431</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -6860,16 +6860,16 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.78</v>
+        <v>1.37</v>
       </c>
       <c r="P81" t="n">
-        <v>0.258</v>
+        <v>0.205</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.414483881527771</v>
+        <v>1.783050864899664</v>
       </c>
       <c r="R81" t="n">
-        <v>1.455051740410974</v>
+        <v>2.112078018665061</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-09-02 09:33:17</t>
+          <t>2025-09-08 15:51:33</t>
         </is>
       </c>
     </row>
